--- a/diseases/d013/1995-1999.xlsx
+++ b/diseases/d013/1995-1999.xlsx
@@ -1943,6 +1943,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2478,6 +2483,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2623,6 +2633,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2768,6 +2783,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2913,6 +2933,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3058,6 +3083,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3203,6 +3233,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3348,6 +3383,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3493,6 +3533,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3638,6 +3683,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3783,6 +3833,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3928,6 +3983,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4463,6 +4523,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4998,6 +5063,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5143,6 +5213,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5288,6 +5363,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5433,6 +5513,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5578,6 +5663,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5723,6 +5813,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5868,6 +5963,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6013,6 +6113,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6158,6 +6263,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6303,6 +6413,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6448,6 +6563,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6983,6 +7103,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7518,6 +7643,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7663,6 +7793,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7808,6 +7943,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7953,6 +8093,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8098,6 +8243,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8243,6 +8393,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8388,6 +8543,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8533,6 +8693,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8678,6 +8843,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8823,6 +8993,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8966,6 +9141,11 @@
       <c r="S53" t="inlineStr">
         <is>
           <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">

--- a/diseases/d013/1995-1999.xlsx
+++ b/diseases/d013/1995-1999.xlsx
@@ -1938,11 +1938,6 @@
       <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1955,22 +1950,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -2085,11 +2070,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
@@ -2107,12 +2087,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -2123,11 +2098,6 @@
       <c r="AT9" t="n">
         <v>1</v>
       </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>is_doh_annual</t>
@@ -2150,22 +2120,22 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -2192,17 +2162,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2227,12 +2197,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>1997-02-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1997-01</t>
+          <t>1997-02</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2241,165 +2211,66 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>Lömunarveiki</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
+      <c r="Q10" t="n">
+        <v>0</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN10" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -2461,12 +2332,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1997-02-01</t>
+          <t>1997-03-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1997-02</t>
+          <t>1997-03</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2478,11 +2349,6 @@
       <c r="Q11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2495,22 +2361,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2611,12 +2467,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1997-03-01</t>
+          <t>1997-04-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1997-03</t>
+          <t>1997-04</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2628,11 +2484,6 @@
       <c r="Q12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2645,22 +2496,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2761,12 +2602,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1997-04-01</t>
+          <t>1997-05-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1997-04</t>
+          <t>1997-05</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2778,11 +2619,6 @@
       <c r="Q13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2795,22 +2631,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2911,12 +2737,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1997-05-01</t>
+          <t>1997-06-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1997-05</t>
+          <t>1997-06</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2928,11 +2754,6 @@
       <c r="Q14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2945,22 +2766,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -3061,12 +2872,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1997-06-01</t>
+          <t>1997-07-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1997-06</t>
+          <t>1997-07</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -3078,11 +2889,6 @@
       <c r="Q15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3095,22 +2901,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -3211,12 +3007,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1997-07-01</t>
+          <t>1997-08-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1997-07</t>
+          <t>1997-08</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3228,11 +3024,6 @@
       <c r="Q16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3245,22 +3036,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3361,12 +3142,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1997-08-01</t>
+          <t>1997-09-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1997-08</t>
+          <t>1997-09</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3378,11 +3159,6 @@
       <c r="Q17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3395,22 +3171,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3511,12 +3277,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1997-09-01</t>
+          <t>1997-10-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1997-09</t>
+          <t>1997-10</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -3528,11 +3294,6 @@
       <c r="Q18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3545,22 +3306,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3661,12 +3412,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1997-10-01</t>
+          <t>1997-11-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1997-10</t>
+          <t>1997-11</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -3678,11 +3429,6 @@
       <c r="Q19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3695,22 +3441,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3811,12 +3547,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1997-11-01</t>
+          <t>1997-12-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1997-11</t>
+          <t>1997-12</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -3828,11 +3564,6 @@
       <c r="Q20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3845,22 +3576,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3931,12 +3652,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3961,12 +3682,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1997-12-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1997-12</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -3975,81 +3696,87 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="S21" t="inlineStr">
         <is>
           <t>missing_population</t>
         </is>
       </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -4076,7 +3803,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4125,20 +3852,98 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
         </is>
       </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN22" t="b">
+        <v>1</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -4232,17 +4037,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -4281,165 +4086,66 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
+      <c r="Q23" t="n">
+        <v>0</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN23" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -4471,12 +4177,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -4515,81 +4221,72 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>missing_population</t>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr"/>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -4621,12 +4318,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4651,12 +4348,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1998-02-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1998-02</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4665,87 +4362,66 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
-        </is>
+      <c r="Q25" t="n">
+        <v>0</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -4772,17 +4448,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4807,12 +4483,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1998-03-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1998-03</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4821,165 +4497,66 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>Lömunarveiki</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
+      <c r="Q26" t="n">
+        <v>0</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG26" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN26" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ26" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS26" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -5041,12 +4618,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1998-02-01</t>
+          <t>1998-04-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1998-02</t>
+          <t>1998-04</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -5058,11 +4635,6 @@
       <c r="Q27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5075,22 +4647,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -5191,12 +4753,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1998-03-01</t>
+          <t>1998-05-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1998-03</t>
+          <t>1998-05</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -5208,11 +4770,6 @@
       <c r="Q28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5225,22 +4782,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -5341,12 +4888,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1998-04-01</t>
+          <t>1998-06-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1998-04</t>
+          <t>1998-06</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5358,11 +4905,6 @@
       <c r="Q29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5375,22 +4917,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5491,12 +5023,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1998-05-01</t>
+          <t>1998-07-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1998-05</t>
+          <t>1998-07</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -5508,11 +5040,6 @@
       <c r="Q30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5525,22 +5052,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5641,12 +5158,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1998-06-01</t>
+          <t>1998-08-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1998-06</t>
+          <t>1998-08</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -5658,11 +5175,6 @@
       <c r="Q31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5675,22 +5187,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5791,12 +5293,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1998-07-01</t>
+          <t>1998-09-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1998-07</t>
+          <t>1998-09</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -5808,11 +5310,6 @@
       <c r="Q32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5825,22 +5322,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5941,12 +5428,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1998-08-01</t>
+          <t>1998-10-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1998-08</t>
+          <t>1998-10</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5958,11 +5445,6 @@
       <c r="Q33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5975,22 +5457,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -6091,12 +5563,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1998-09-01</t>
+          <t>1998-11-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1998-09</t>
+          <t>1998-11</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -6108,11 +5580,6 @@
       <c r="Q34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6125,22 +5592,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -6241,12 +5698,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1998-10-01</t>
+          <t>1998-12-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1998-10</t>
+          <t>1998-12</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -6258,11 +5715,6 @@
       <c r="Q35" t="n">
         <v>0</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6275,22 +5727,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -6361,12 +5803,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -6391,12 +5833,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1998-11-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1998-11</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -6405,81 +5847,87 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6506,17 +5954,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -6541,12 +5989,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1998-12-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1998-12</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -6555,81 +6003,165 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>missing_population</t>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN37" t="b">
+        <v>1</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6661,12 +6193,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -6705,87 +6237,66 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
-        </is>
+      <c r="Q38" t="n">
+        <v>0</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ38" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS38" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -6812,17 +6323,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6863,32 +6374,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
+          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6896,64 +6382,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG39" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN39" t="b">
-        <v>1</v>
-      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -6961,65 +6389,55 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ39" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT39" t="n">
         <v>1</v>
       </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -7081,12 +6499,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1999-02-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -7098,11 +6516,6 @@
       <c r="Q40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7115,22 +6528,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -7201,12 +6604,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -7231,12 +6634,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1999-03-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1999-03</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -7245,87 +6648,66 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
-        </is>
+      <c r="Q41" t="n">
+        <v>0</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ41" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7352,17 +6734,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -7387,12 +6769,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1999-04-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -7401,165 +6783,66 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>Lömunarveiki</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
+      <c r="Q42" t="n">
+        <v>0</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD42" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG42" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN42" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ42" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS42" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7621,12 +6904,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1999-02-01</t>
+          <t>1999-05-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1999-05</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7638,11 +6921,6 @@
       <c r="Q43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7655,22 +6933,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7771,12 +7039,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1999-03-01</t>
+          <t>1999-06-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1999-06</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7788,11 +7056,6 @@
       <c r="Q44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7805,22 +7068,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7921,12 +7174,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1999-04-01</t>
+          <t>1999-07-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1999-07</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7938,11 +7191,6 @@
       <c r="Q45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7955,22 +7203,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -8071,12 +7309,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1999-05-01</t>
+          <t>1999-08-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1999-08</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -8088,11 +7326,6 @@
       <c r="Q46" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8105,22 +7338,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -8221,12 +7444,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1999-06-01</t>
+          <t>1999-09-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1999-09</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -8238,11 +7461,6 @@
       <c r="Q47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8255,22 +7473,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -8371,12 +7579,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1999-07-01</t>
+          <t>1999-10-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1999-07</t>
+          <t>1999-10</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -8388,11 +7596,6 @@
       <c r="Q48" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8405,22 +7608,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -8521,12 +7714,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1999-08-01</t>
+          <t>1999-11-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1999-08</t>
+          <t>1999-11</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -8538,11 +7731,6 @@
       <c r="Q49" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8555,22 +7743,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8671,12 +7849,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1999-12-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1999-09</t>
+          <t>1999-12</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -8688,11 +7866,6 @@
       <c r="Q50" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8705,23 +7878,13 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
       </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV50" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -8758,456 +7921,6 @@
         </is>
       </c>
       <c r="BC50" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>D013</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>poliomyelitis</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>D013</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>脊髓灰质炎</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>1999-10-01</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>1999-10</t>
-        </is>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP51" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr"/>
-      <c r="AT51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV51" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA51" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB51" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC51" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>D013</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>poliomyelitis</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>D013</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>脊髓灰质炎</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>1999-11-01</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>1999-11</t>
-        </is>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP52" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr"/>
-      <c r="AT52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV52" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA52" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB52" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC52" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>D013</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>poliomyelitis</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>D013</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>脊髓灰质炎</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>1999-12-01</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>1999-12</t>
-        </is>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP53" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr"/>
-      <c r="AT53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV53" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA53" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB53" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC53" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -9339,7 +8052,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11">
@@ -9359,7 +8072,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -9369,7 +8082,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d013/1995-1999.xlsx
+++ b/diseases/d013/1995-1999.xlsx
@@ -2070,6 +2070,11 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
@@ -2087,7 +2092,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -2098,6 +2108,11 @@
       <c r="AT9" t="n">
         <v>1</v>
       </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>is_doh_annual</t>
@@ -2120,22 +2135,22 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -2162,17 +2177,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2197,12 +2212,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1997-02-01</t>
+          <t>1997-01-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1997-02</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2211,66 +2226,165 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Lömunarveiki</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN10" t="b">
+        <v>1</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -2332,12 +2446,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1997-03-01</t>
+          <t>1997-02-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1997-03</t>
+          <t>1997-02</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2467,12 +2581,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1997-04-01</t>
+          <t>1997-03-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1997-04</t>
+          <t>1997-03</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2602,12 +2716,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1997-05-01</t>
+          <t>1997-04-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1997-05</t>
+          <t>1997-04</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2737,12 +2851,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1997-06-01</t>
+          <t>1997-05-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1997-06</t>
+          <t>1997-05</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2872,12 +2986,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1997-07-01</t>
+          <t>1997-06-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1997-07</t>
+          <t>1997-06</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -3007,12 +3121,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1997-08-01</t>
+          <t>1997-07-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1997-08</t>
+          <t>1997-07</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3142,12 +3256,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1997-09-01</t>
+          <t>1997-08-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1997-09</t>
+          <t>1997-08</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3277,12 +3391,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1997-10-01</t>
+          <t>1997-09-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1997-10</t>
+          <t>1997-09</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -3412,12 +3526,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1997-11-01</t>
+          <t>1997-10-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1997-11</t>
+          <t>1997-10</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -3547,12 +3661,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1997-12-01</t>
+          <t>1997-11-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1997-12</t>
+          <t>1997-11</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -3652,12 +3766,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3682,12 +3796,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
+          <t>1997-12-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1998-01</t>
+          <t>1997-12</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -3696,87 +3810,66 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
-        </is>
+      <c r="Q21" t="n">
+        <v>0</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3896,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3852,98 +3945,20 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN22" t="b">
-        <v>1</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -4037,17 +4052,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -4086,66 +4101,165 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN23" t="b">
+        <v>1</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -4177,12 +4291,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -4221,19 +4335,17 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
-        </is>
+      <c r="Q24" t="n">
+        <v>0</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
@@ -4241,52 +4353,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS24" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
-        </is>
-      </c>
+      <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -4318,12 +4426,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4348,12 +4456,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1998-02-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1998-02</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4362,66 +4470,87 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
+        </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -4448,17 +4577,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4483,12 +4612,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1998-03-01</t>
+          <t>1998-01-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1998-03</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4497,66 +4626,165 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Lömunarveiki</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN26" t="b">
+        <v>1</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS26" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -4618,12 +4846,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1998-04-01</t>
+          <t>1998-02-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1998-04</t>
+          <t>1998-02</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4753,12 +4981,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1998-05-01</t>
+          <t>1998-03-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1998-05</t>
+          <t>1998-03</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -4888,12 +5116,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1998-06-01</t>
+          <t>1998-04-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1998-06</t>
+          <t>1998-04</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5023,12 +5251,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1998-07-01</t>
+          <t>1998-05-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1998-07</t>
+          <t>1998-05</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -5158,12 +5386,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1998-08-01</t>
+          <t>1998-06-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1998-08</t>
+          <t>1998-06</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -5293,12 +5521,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1998-09-01</t>
+          <t>1998-07-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1998-09</t>
+          <t>1998-07</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -5428,12 +5656,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1998-10-01</t>
+          <t>1998-08-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1998-10</t>
+          <t>1998-08</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5563,12 +5791,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1998-11-01</t>
+          <t>1998-09-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1998-11</t>
+          <t>1998-09</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -5698,12 +5926,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1998-12-01</t>
+          <t>1998-10-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1998-12</t>
+          <t>1998-10</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -5803,12 +6031,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5833,12 +6061,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1998-11-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1998-11</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -5847,87 +6075,66 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
-        </is>
+      <c r="Q36" t="n">
+        <v>0</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ36" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -5954,17 +6161,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5989,12 +6196,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1998-12-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1998-12</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -6003,165 +6210,66 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>Poliomyelitis</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
-        </is>
+      <c r="Q37" t="n">
+        <v>0</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG37" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN37" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ37" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -6193,12 +6301,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -6237,66 +6345,87 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS38" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6323,17 +6452,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6374,7 +6503,32 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6382,6 +6536,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN39" t="b">
+        <v>1</v>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -6389,55 +6601,65 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D94_ANNUAL</t>
         </is>
       </c>
       <c r="AT39" t="n">
         <v>1</v>
       </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6499,12 +6721,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1999-02-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6604,12 +6826,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -6634,12 +6856,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1999-03-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -6648,66 +6870,87 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
+        </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -6734,17 +6977,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6769,12 +7012,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1999-04-01</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1999-01</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -6783,66 +7026,165 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Lömunarveiki</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN42" t="b">
+        <v>1</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS42" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_POLIOMYELITIS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -6904,12 +7246,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1999-05-01</t>
+          <t>1999-02-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7039,12 +7381,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1999-06-01</t>
+          <t>1999-03-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1999-03</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7174,12 +7516,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1999-07-01</t>
+          <t>1999-04-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1999-07</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7309,12 +7651,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1999-08-01</t>
+          <t>1999-05-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1999-08</t>
+          <t>1999-05</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7444,12 +7786,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1999-06-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1999-09</t>
+          <t>1999-06</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7579,12 +7921,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1999-10-01</t>
+          <t>1999-07-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1999-10</t>
+          <t>1999-07</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -7714,12 +8056,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1999-11-01</t>
+          <t>1999-08-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1999-11</t>
+          <t>1999-08</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -7849,12 +8191,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1999-12-01</t>
+          <t>1999-09-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1999-12</t>
+          <t>1999-09</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -7921,6 +8263,411 @@
         </is>
       </c>
       <c r="BC50" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>1999-10-01</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>1999-10</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>1999-11-01</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>1999-11</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>poliomyelitis</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1999-12-01</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1999-12</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -8052,7 +8799,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -8072,7 +8819,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -8082,7 +8829,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d013/1995-1999.xlsx
+++ b/diseases/d013/1995-1999.xlsx
@@ -1938,6 +1938,11 @@
       <c r="Q8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1950,12 +1955,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -2463,6 +2478,11 @@
       <c r="Q11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2475,12 +2495,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2598,6 +2628,11 @@
       <c r="Q12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2610,12 +2645,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2733,6 +2778,11 @@
       <c r="Q13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2745,12 +2795,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2868,6 +2928,11 @@
       <c r="Q14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2880,12 +2945,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -3003,6 +3078,11 @@
       <c r="Q15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3015,12 +3095,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -3138,6 +3228,11 @@
       <c r="Q16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3150,12 +3245,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3273,6 +3378,11 @@
       <c r="Q17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3285,12 +3395,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3408,6 +3528,11 @@
       <c r="Q18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3420,12 +3545,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3543,6 +3678,11 @@
       <c r="Q19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3555,12 +3695,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3678,6 +3828,11 @@
       <c r="Q20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3690,12 +3845,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3813,6 +3978,11 @@
       <c r="Q21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3825,12 +3995,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -4338,6 +4518,11 @@
       <c r="Q24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4350,12 +4535,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4863,6 +5058,11 @@
       <c r="Q27" t="n">
         <v>0</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4875,12 +5075,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4998,6 +5208,11 @@
       <c r="Q28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5010,12 +5225,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -5133,6 +5358,11 @@
       <c r="Q29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5145,12 +5375,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5268,6 +5508,11 @@
       <c r="Q30" t="n">
         <v>0</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5280,12 +5525,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5403,6 +5658,11 @@
       <c r="Q31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5415,12 +5675,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5538,6 +5808,11 @@
       <c r="Q32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5550,12 +5825,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5673,6 +5958,11 @@
       <c r="Q33" t="n">
         <v>0</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5685,12 +5975,22 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5808,6 +6108,11 @@
       <c r="Q34" t="n">
         <v>0</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5820,12 +6125,22 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5943,6 +6258,11 @@
       <c r="Q35" t="n">
         <v>0</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5955,12 +6275,22 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -6078,6 +6408,11 @@
       <c r="Q36" t="n">
         <v>0</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6090,12 +6425,22 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6213,6 +6558,11 @@
       <c r="Q37" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6225,12 +6575,22 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6738,6 +7098,11 @@
       <c r="Q40" t="n">
         <v>0</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6750,12 +7115,22 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -7263,6 +7638,11 @@
       <c r="Q43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7275,12 +7655,22 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7398,6 +7788,11 @@
       <c r="Q44" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7410,12 +7805,22 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7533,6 +7938,11 @@
       <c r="Q45" t="n">
         <v>0</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7545,12 +7955,22 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7668,6 +8088,11 @@
       <c r="Q46" t="n">
         <v>0</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7680,12 +8105,22 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7803,6 +8238,11 @@
       <c r="Q47" t="n">
         <v>0</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7815,12 +8255,22 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7938,6 +8388,11 @@
       <c r="Q48" t="n">
         <v>0</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7950,12 +8405,22 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -8073,6 +8538,11 @@
       <c r="Q49" t="n">
         <v>0</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8085,12 +8555,22 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8208,6 +8688,11 @@
       <c r="Q50" t="n">
         <v>0</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8220,12 +8705,22 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8343,6 +8838,11 @@
       <c r="Q51" t="n">
         <v>0</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8355,12 +8855,22 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8478,6 +8988,11 @@
       <c r="Q52" t="n">
         <v>0</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8490,12 +9005,22 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8613,6 +9138,11 @@
       <c r="Q53" t="n">
         <v>0</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8625,12 +9155,22 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
